--- a/www/download/COUNTRY.ESP.rpPE.xlsx
+++ b/www/download/COUNTRY.ESP.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.748755221325691</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.760965480792957</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.878796386756267</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.896619689745689</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.938262371071927</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1.082719769858</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1.11656987802902</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1.05752963938752</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.884017003011732</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0.80392318278615</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.803793923544842</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>0.7964320001188</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.729660724615538</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074660125</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948693257338</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.569</t>
+          <t>-0.186622123351465</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.796</t>
+          <t>-0.168402524726333</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.293</t>
+          <t>-0.0629914822362037</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.932</t>
+          <t>-0.0433201870115424</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.617</t>
+          <t>0.032170745536414</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16.412</t>
+          <t>0.228003747343914</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.931</t>
+          <t>0.19164754121372</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.338</t>
+          <t>0.110069787337133</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17.878</t>
+          <t>0.00765493420968122</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>-0.0858978026613323</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19.267</t>
+          <t>-0.0651576716370508</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20.022</t>
+          <t>-0.0584791584376148</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.628</t>
+          <t>-0.0953063535866328</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20.576</t>
+          <t>-0.139738408901628</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>19.258</t>
+          <t>-0.155533182950752</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11.022</t>
+          <t>-0.417081180983975</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.232</t>
+          <t>-0.414821965990692</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.825</t>
+          <t>-0.350006456962168</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>-0.355209891447194</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>-0.308731808910633</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.815</t>
+          <t>-0.225314438053865</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.285</t>
+          <t>-0.241773514079062</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.666</t>
+          <t>-0.292427469874434</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.204</t>
+          <t>-0.352056167068656</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15.763</t>
+          <t>-0.424794701553773</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16.458</t>
+          <t>-0.415453604896019</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>-0.420042622308616</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>17.759</t>
+          <t>-0.430400292190029</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>17.695</t>
+          <t>-0.458408294344314</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.561</t>
+          <t>-0.474350677324447</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23514.494</t>
+          <t>-0.766420943203382</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23846.269</t>
+          <t>-0.763715972041425</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24704.464</t>
+          <t>-0.73965343246859</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25856.859</t>
+          <t>-0.752161252406543</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27049.908</t>
+          <t>-0.741804393446638</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28401.149</t>
+          <t>-0.727585195717893</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29231.75</t>
+          <t>-0.73435885771834</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29836.085</t>
+          <t>-0.749066666834311</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30494.884</t>
+          <t>-0.791489807642261</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31273.815</t>
+          <t>-0.786067860450953</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>32133.3</t>
+          <t>-0.77791369815215</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>33146.634</t>
+          <t>-0.774120467217659</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>33757.146</t>
+          <t>-0.769665812508285</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>33692.434</t>
+          <t>-0.769836191912418</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>31673.494</t>
+          <t>-0.77725803558741</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18384.955</t>
+          <t>92848639072.3142</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18810.323</t>
+          <t>95469692286.1652</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19852.46</t>
+          <t>93592672560.3688</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20871.514</t>
+          <t>106208191296.209</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22043.548</t>
+          <t>118618548103.448</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23299.203</t>
+          <t>136476001413.811</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24047.748</t>
+          <t>139588007869.798</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24668.354</t>
+          <t>146939651439.145</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25346.447</t>
+          <t>140001942157.937</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26060.341</t>
+          <t>155255534843.654</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>26899.087</t>
+          <t>162274585363.07</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27871.875</t>
+          <t>166875495644.687</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28470.212</t>
+          <t>161263014129.124</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>28549.186</t>
+          <t>147618320492.539</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26760.757</t>
+          <t>123746969194.524</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>100416110182.299</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>102477915445.054</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>98293433029.858</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>109217226049.822</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>111212258773.234</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>109529468772.638</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>117181877175.018</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>127956569133.445</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>141550334630.424</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>159189783187.352</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>158979933352.72</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>160569125827.037</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>159473119489.44</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>160924617914.909</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>157894669061.949</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>3158270.53751443</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>3157888.01354504</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>3420939.06362432</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>3759861.17784804</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>4197273.94002416</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>5027449.6066308</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>4857655.20827285</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>4505215.67932019</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>3418898.99069147</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>3231896.52174735</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>3046984.86522966</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>2866891.76919256</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>2379140.25239491</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>1908563.42439206</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>1848096.03199591</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>127046.160667281</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>134974.989168819</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>139750.814141308</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.72</t>
+          <t>148675.877330131</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>162653.668397969</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>177881.439228511</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>177573.057767999</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>187794.918588855</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>205340.092493065</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>229904.881303855</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>257577.605635101</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>277438.512356248</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>313356.959383847</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>332956.491382533</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>290017.690613198</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>50.22</t>
+          <t>306347.134030943</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>318647.798017745</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>305625.325385521</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>329041.618187253</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>372041.402635058</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>60.53</t>
+          <t>416446.989161156</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>61.63</t>
+          <t>410875.240315292</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>62.55</t>
+          <t>444064.01402887</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>62.18</t>
+          <t>490524.320562914</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>565081.387530703</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>639948.980236301</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>63.68</t>
+          <t>699777.70344674</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>799334.702570303</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>831384.634596738</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>641998.670836341</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>-0.503407353257099</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>-0.481211629290372</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>-0.414724271475866</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>-0.405100445242544</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>-0.354361085287388</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>-0.241195984832408</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>-0.24935932076598</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>-0.293026115890029</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>-0.390226537337657</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>-0.405960008094677</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>-0.381183867377623</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>-0.377526763033722</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>-0.392200952912184</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>-0.413812470342084</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>-0.414732046526756</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>111897.430452834</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>117807.171481491</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>108524.751577177</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>111980.262251848</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>114414.474727125</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>111181.561355402</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>113379.834332325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>126635.044450346</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>163392.96590868</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>193063.439321445</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>207955.822676289</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>226159.555082345</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>267551.938753399</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.748755221325691</t>
+          <t>9110.59726191528</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.760965480792957</t>
+          <t>9124.07096451569</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.878796386756267</t>
+          <t>8312.27076556291</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.896619689745689</t>
+          <t>8801.02711206017</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262371071927</t>
+          <t>8505.32543495193</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.082719769858</t>
+          <t>7928.47248023031</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987802902</t>
+          <t>8203.31383753371</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963938752</t>
+          <t>8724.58913238913</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017003011732</t>
+          <t>9310.25570291598</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.80392318278615</t>
+          <t>10099.0803148775</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923544842</t>
+          <t>9659.73589456311</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.7964320001188</t>
+          <t>9346.17325916096</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724615538</t>
+          <t>8979.89850100174</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074660125</t>
+          <t>9094.5609346868</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948693257338</t>
+          <t>9533.83866569746</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>24068840453.2853</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>24055763029.4746</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>18811839789.3635</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>22068276033.191</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>23821558188.3981</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>25292589345.3312</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>29857566743.375</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>34614681914.2306</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>36422834841.4169</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>39750802761.1338</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>39042347921.2642</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>39146409555.0338</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>38603035406.5287</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>42818864889.8743</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>39513712681.6446</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>25541417218.0328</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>25452221463.7267</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>20024512557.5128</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>23489984099.3132</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>25434446866.851</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>27564321236.933</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>32458273983.4207</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>37000364572.2899</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>39189853991.8033</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>43475074039.2711</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>42112634300.6835</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>42751610202.873</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>42417152798.2987</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>46077149039.1497</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>42230592785.6848</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>-1472576764.7475</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>-1396458434.25209</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>-1212672768.14925</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>-1421708066.12221</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.095</t>
+          <t>-1612888678.45295</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.023</t>
+          <t>-2271731891.6018</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>-2600707240.04567</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.449</t>
+          <t>-2385682658.05929</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.214</t>
+          <t>-2767019150.38644</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.893</t>
+          <t>-3724271278.13737</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>-3070286379.4193</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.685</t>
+          <t>-3605200647.83916</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5.504</t>
+          <t>-3814117391.77001</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3258284149.27534</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2716880104.0402</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>4524.25560770314</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>4733.46190992012</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.085</t>
+          <t>4864.97032800469</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>5235.72711037289</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>5491.36908309993</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>6016.15675214452</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>6157.74107097614</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>6168.05666618878</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.695</t>
+          <t>5677.14685823891</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>5999.25758850107</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>5977.6004084271</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>5817.74272187759</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.839</t>
+          <t>5457.97375185417</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>5331.11820762744</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>5579.85024461684</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>5619.05439274613</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>5832.39496465301</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>5989.36585402758</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>6489.69343754177</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>6796.63409988115</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>7297.30406856884</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>7457.04369439918</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>7417.58905192476</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>6785.27450832804</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>7164.44220130379</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>7135.44793298867</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>6947.84425860686</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>6494.74821056943</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>6272.03162462249</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>6558.29772641549</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>109520.280260737</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>121019.906945021</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>125440.923317723</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>132596.03965942</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>134697.557195567</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>140903.507170301</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>144886.601118099</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>158476.850079172</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>195988.313768716</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>229314.211284507</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>245985.920616821</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>278285.203619124</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>334952.87473209</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>366573.171549866</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>293688.174509799</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-41.71</t>
+          <t>11609965690.5921</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-41.48</t>
+          <t>12695188001.3871</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>14129886855.1033</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>16471228252.2534</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-30.87</t>
+          <t>18253685848.8199</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-22.53</t>
+          <t>22819215133.2806</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>22773517569.2281</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-29.24</t>
+          <t>23106272646.7678</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>22023666314.6421</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-42.48</t>
+          <t>24816553143.0065</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>25206811561.6804</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-42</t>
+          <t>27327526382.4465</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>27382268544.7047</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-45.84</t>
+          <t>25567586907.7389</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>18954060415.8854</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-76.64</t>
+          <t>124770.118251857</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-76.37</t>
+          <t>133889.711107774</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-73.97</t>
+          <t>135377.567732083</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-75.22</t>
+          <t>150396.284162831</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-74.18</t>
+          <t>164268.961420969</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-72.76</t>
+          <t>175674.697712927</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-73.44</t>
+          <t>177717.690062476</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-74.91</t>
+          <t>190692.877611322</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-79.15</t>
+          <t>238769.467007788</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-78.61</t>
+          <t>293693.971671943</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>326928.67876476</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-77.41</t>
+          <t>377946.471463735</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>453611.854891462</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-76.98</t>
+          <t>483950.566419665</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-77.73</t>
+          <t>350325.246453118</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>76246.64</t>
+          <t>41557738208.9928</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>80463.715</t>
+          <t>41542003738.6653</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>85607.809</t>
+          <t>36397062844.2734</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>96904.102</t>
+          <t>45415800609.4992</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>106143.708</t>
+          <t>54194375810.0494</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>119759.706</t>
+          <t>63171492744.9258</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>126252.224</t>
+          <t>67682830854.7392</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>128603.192</t>
+          <t>72251375024.2906</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>121304.424</t>
+          <t>75248925357.2401</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>132612.392</t>
+          <t>89054943403.9921</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>137480.816</t>
+          <t>92359840044.4285</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>139109.738</t>
+          <t>97580922668.3159</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>133976.913</t>
+          <t>97094213638.5854</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>129055.312</t>
+          <t>95131955239.8497</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>126297.899</t>
+          <t>72916177900.843</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49865.902</t>
+          <t>-15249.8379911202</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>53164.351</t>
+          <t>-12869.8041627527</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>57528.761</t>
+          <t>-9936.64441436082</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>64973.279</t>
+          <t>-17800.2445034108</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>71802.962</t>
+          <t>-29571.4042254017</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>83111.401</t>
+          <t>-34771.1905426264</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>87961.484</t>
+          <t>-32831.0889443763</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>90461.953</t>
+          <t>-32216.0275321508</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>86313.638</t>
+          <t>-42781.1532390726</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>94565.098</t>
+          <t>-64379.7603874361</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>98379.348</t>
+          <t>-80942.7581479387</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>99949.984</t>
+          <t>-99661.2678446112</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>96927.61</t>
+          <t>-118658.980159372</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>94332.004</t>
+          <t>-117377.394869799</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>92410.69</t>
+          <t>-56637.0719433188</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>92848.639</t>
+          <t>-29947772518.4007</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>95469.692</t>
+          <t>-28846815737.2782</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>93592.673</t>
+          <t>-22267175989.1701</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>106208.191</t>
+          <t>-28944572357.2458</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>118618.548</t>
+          <t>-35940689961.2295</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>136476.001</t>
+          <t>-40352277611.6451</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>139588.008</t>
+          <t>-44909313285.5111</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>146939.651</t>
+          <t>-49145102377.5228</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>140001.942</t>
+          <t>-53225259042.598</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>155255.535</t>
+          <t>-64238390260.9856</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>162274.585</t>
+          <t>-67153028482.7481</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>166875.496</t>
+          <t>-70253396285.8694</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>161263.014</t>
+          <t>-69711945093.8807</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>147618.32</t>
+          <t>-69564368332.1108</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>123746.969</t>
+          <t>-53962117484.9576</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>266375.37769</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>278035.05396</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>252297.51342</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>260955.44354</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>263350.98525</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>246557.79417</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>257872.79854</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>288378.67913</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>369600.35736</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>433637.20248</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>466138.1344</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>503621.1502</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>585940.81553</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>654300.10674</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>591298.93665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>38505.544</t>
+          <t>0.0382210135319761</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>40439.698</t>
+          <t>0.0379299984927473</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42796.362</t>
+          <t>0.0371796406325024</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>47989.662</t>
+          <t>0.0383553601013954</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>51859.126</t>
+          <t>0.0377885410089678</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>58294.448</t>
+          <t>0.0379940731320384</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>60327.484</t>
+          <t>0.0416998527072626</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>62140.86</t>
+          <t>0.0433946513048132</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>58606.7</t>
+          <t>0.0429779092718767</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>63166.132</t>
+          <t>0.0434680078153492</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>65315.049</t>
+          <t>0.0433471913371612</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>66160.566</t>
+          <t>0.0430494340166089</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>63218.684</t>
+          <t>0.0426223933143097</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>59118.819</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>55901.689</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>291808.316733849</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>305132.106559137</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>284654.105695089</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>297978.063926283</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>306337.553877687</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>288325.761286174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>299763.592259955</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>335934.791999997</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>428228.190224466</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>498930.754307214</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>535998.080271348</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>583286.457455248</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>688240.415189618</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>783200.673539864</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>727079.091269295</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>100416.11</t>
+          <t>358083.445359631</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>102477.915</t>
+          <t>372331.088725999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>98293.433</t>
+          <t>342997.313917794</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>109217.226</t>
+          <t>358380.819232282</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>111212.259</t>
+          <t>366035.373843655</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>109529.469</t>
+          <t>338929.567248008</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>117181.877</t>
+          <t>351984.377498107</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>127956.569</t>
+          <t>392605.991558936</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>141550.335</t>
+          <t>498162.302385956</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>159189.783</t>
+          <t>578956.463825489</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>158979.933</t>
+          <t>620027.285849691</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>160569.126</t>
+          <t>673117.318416295</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>159473.119</t>
+          <t>792753.100788172</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>160924.618</t>
+          <t>902445.44325516</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>157894.669</t>
+          <t>835809.727677538</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>2112166.5018118</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-48.12</t>
+          <t>2180500.62823819</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>1985902.06707059</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>2034912.54597896</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-35.44</t>
+          <t>2095213.63527716</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-24.12</t>
+          <t>2022897.09422545</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>2118527.5765778</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-29.3</t>
+          <t>2449366.85224449</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-39.02</t>
+          <t>3213887.97397246</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-40.6</t>
+          <t>3892532.23570367</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>4254845.27958112</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>4684517.58514539</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-39.22</t>
+          <t>5503591.05807592</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-41.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>358083.445359631</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>365829.935846962</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>381569.691012317</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>397102.440614817</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.197</t>
+          <t>414710.268884059</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.027</t>
+          <t>427270.86837679</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.858</t>
+          <t>437485.250962429</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.505</t>
+          <t>442468.031891349</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.419</t>
+          <t>451075.692171595</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.232</t>
+          <t>459626.088998396</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>473503.168458034</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.867</t>
+          <t>492135.084105528</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.379</t>
+          <t>511999.508728918</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>520129.075526616</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.848</t>
+          <t>497819.439729837</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>291808.316733849</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>299450.510346145</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>316084.751467274</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>329625.822547258</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>346500.191208835</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>363089.5603355</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>372924.047543774</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>378930.134595833</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>388669.644566182</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>396925.803602501</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>410391.417042076</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>426629.233357581</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>444414.086390273</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>450928.707152788</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>431377.285263621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>192626.574900369</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>200513.557024001</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>182359.876762206</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>190030.065727718</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>193589.541106345</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>188039.661491992</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>201722.122231893</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>232924.464921064</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>301519.151664044</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>362264.060964511</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>392391.415120309</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>427825.385763705</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>502128.161471828</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>562487.57750484</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>530674.386332462</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>49865901931.0544</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>53164350787.4588</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>57528760625.6883</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>64973279148.8834</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>71802962057.0888</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>83111400683.8509</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>87961483876.5729</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>90461952677.6579</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>86313637688.6069</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>94565097516.0246</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>98379347521.8933</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>99949983510.4014</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>96927610061.803</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>94332004236.6846</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>92410689826.2218</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>76246640390.2482</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>80463715101.0775</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>85607808951.7309</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>96904102409.031</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>106143707604.145</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>119759705721.317</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>126252223972.395</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>128603191946.651</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>121304423550.085</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>132612392257.693</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>137480815959.273</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>139109737745.827</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>133976913461.732</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>129055312073.648</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>126297899404.134</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>38505544223.9853</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>40439697880.9752</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>42796362413.5974</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>47989661938.825</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>51859126033.8631</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>58294448473.6002</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>60327483754.3451</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>62140860343.831</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>58606700110.0555</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>63166131636.3164</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>65315049236.9161</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>66160566466.0866</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>63218683745.4767</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>59118819388.3548</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>55901689296.9971</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>13569300.9999473</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13795999.000192</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14293301.0001657</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>14931999.9999472</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15617098.9999302</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16411500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>16930600</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17337600</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>17877600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>18509800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>19267300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>20022000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20628500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>20576317.1803866</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>19257725.8112927</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>11021902</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11231600</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11825100</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12409600</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>13075603</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13814700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14284700</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14666200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>15203700</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>15762800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16458000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>17180200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>17758900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>17694600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16561500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>23514493699.9123</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>23846269000.3119</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24704463700.2885</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>25856858599.9331</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>27049908499.8955</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28401148900</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29231750000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>29836085000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>30494883600</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>31273815100</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>32133300400</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>33146633700</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>33757145700</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>33692434300.156</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>31673493566.3532</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>18384954800</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>18810322900</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19852460200</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>20871513900</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22043548100</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23299203000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24047748300</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24668354200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>25346447300</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>26060341300</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>26899086800</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>27871875300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>28470211500</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>28549185900</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>26760757000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.27337934115787</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.293012019827709</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.299484675333469</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.316421547069308</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.325520561365048</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.344668661286352</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.356745111723183</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.366531484113573</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.33902574594464</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.377072787961434</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.389438216927018</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.392341691075884</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.393971012044968</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.392324552249411</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.406426619648174</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.161798090887162</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.171762080787493</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.179831615394149</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.186337128429743</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.190972227950267</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.195922528300967</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.195522472732045</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.19724866341156</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.183891902154676</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.211860667773598</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.226658017483415</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.233821687109926</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.233229578689497</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.237976856018813</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.234416934733873</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.564822567954968</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.535225899384799</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.520683709272383</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.497241324500948</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.483507210684685</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.459408810412681</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.447732415544772</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.436219852474868</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.477082351900684</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.411066544264968</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.383903765589567</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.37383662181419</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.372799409265536</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.369698591731777</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.359156445617952</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.502212188839657</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.526594559913063</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.532620188756776</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.563416504507071</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.577467354823664</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.605268724936211</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.616308415893106</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.625489173903498</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.621783742025194</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.631171986416589</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.635649537039609</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.636768471379647</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.631919201015457</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.628543427804054</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.644977705921931</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.206890735754316</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.208497526577858</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.214584050460499</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.213599178388591</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.215612572954155</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.212142590032889</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.208744709413346</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.206556563835731</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.205146379332471</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.21140452585859</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.218895487693063</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.22059498223511</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.221202643349471</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.220580621626342</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.212471156690214</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.290897075406028</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.264907913509078</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.252795760782724</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.222984317104338</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.206920072222181</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.1825886850309</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.174946874693548</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.167954262260771</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.173069878642335</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.157423487724821</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.145454975267328</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.142636546385243</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.146878155635072</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.150875950569604</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.142551137387855</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1137233.09765</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1180804.65846</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1084757.01577</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1131351.21011</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1157813.60464</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1103652.15177</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1159249.44985</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1325268.7549</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1695348.59695</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2010355.01228</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2200858.88681</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2435198.48464</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2838946.82881</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3191602.43002</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2909046.49266</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>550710.02026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>572844.64575</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>525357.19068</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>548410.88496</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>559624.91495</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>526969.22874</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>553706.49973</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>625530.45648</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>799681.45405</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>941220.52479</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1012418.70097</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1100942.70418</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1294881.26226</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1464933.02076</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1366484.11401</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1581495.68696843</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1628629.82506667</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1680335.50608497</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1742909.88908419</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1816023.17662004</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1895094.92228355</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1977427.19883719</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2059411.54591606</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2146976.35014075</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2239591.37491869</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2341608.52453285</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2454893.7597595</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2578693.7714082</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
